--- a/data/trans_orig/IP18_E_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP18_E_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81373</t>
+          <t>81679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92545</t>
+          <t>92621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83697</t>
+          <t>84177</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80218</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89660</t>
+          <t>89406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166787</t>
+          <t>166433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177421</t>
+          <t>177558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54961</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61866</t>
+          <t>61868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60889</t>
+          <t>61475</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119170</t>
+          <t>118984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127485</t>
+          <t>127114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57651</t>
+          <t>57228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>65176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56240</t>
+          <t>56330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63845</t>
+          <t>63874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117424</t>
+          <t>117559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127641</t>
+          <t>127802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25724</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54835</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60296</t>
+          <t>60299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41764</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47926</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43531</t>
+          <t>43353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87343</t>
+          <t>87599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96197</t>
+          <t>96396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102106</t>
+          <t>102408</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>112787</t>
+          <t>113420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106850</t>
+          <t>106147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116480</t>
+          <t>116475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>213309</t>
+          <t>213604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>227825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>28783</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109657</t>
+          <t>110057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117268</t>
+          <t>117383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122245</t>
+          <t>122106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128995</t>
+          <t>128993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>235150</t>
+          <t>234841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245082</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>559408</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>579694</t>
+          <t>579792</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1106523</t>
+          <t>1106063</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1134395</t>
+          <t>1134911</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67912</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95784</t>
+          <t>96244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>46595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53390</t>
+          <t>53411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56451</t>
+          <t>56870</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61540</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106633</t>
+          <t>106194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>114198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83529</t>
+          <t>83591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91970</t>
+          <t>92158</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83916</t>
+          <t>83712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93362</t>
+          <t>93394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171642</t>
+          <t>170639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>184166</t>
+          <t>183680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>22123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57320</t>
+          <t>56728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63761</t>
+          <t>63774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>62705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122315</t>
+          <t>121764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131468</t>
+          <t>131563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71903</t>
+          <t>71911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74621</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>144323</t>
+          <t>144512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150456</t>
+          <t>150459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>36848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41937</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74857</t>
+          <t>74668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>81397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57401</t>
+          <t>57398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102600</t>
+          <t>103094</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110990</t>
+          <t>111171</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115985</t>
+          <t>114863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126383</t>
+          <t>126257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129004</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138471</t>
+          <t>139145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248781</t>
+          <t>248746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262778</t>
+          <t>263185</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140435</t>
+          <t>140656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148560</t>
+          <t>148441</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>143346</t>
+          <t>142518</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153038</t>
+          <t>153375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>286476</t>
+          <t>287856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>299460</t>
+          <t>299732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>661538</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>682374</t>
+          <t>682051</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1290435</t>
+          <t>1291657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1318748</t>
+          <t>1317988</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>86157</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>49207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48211</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55432</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92803</t>
+          <t>92388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103316</t>
+          <t>103180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83292</t>
+          <t>84068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89172</t>
+          <t>89190</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>89656</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176204</t>
+          <t>175953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182970</t>
+          <t>182915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58145</t>
+          <t>57542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65216</t>
+          <t>65224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52925</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60190</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113728</t>
+          <t>113551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124186</t>
+          <t>123903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71212</t>
+          <t>71176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67297</t>
+          <t>67882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75706</t>
+          <t>75791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136291</t>
+          <t>136005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145945</t>
+          <t>145721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>36361</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40647</t>
+          <t>41143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80102</t>
+          <t>79720</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85470</t>
+          <t>85468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46412</t>
+          <t>46556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>95515</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103393</t>
+          <t>103368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100375</t>
+          <t>100716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108729</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105614</t>
+          <t>105831</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112187</t>
+          <t>112202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>209343</t>
+          <t>208926</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219390</t>
+          <t>219064</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141860</t>
+          <t>141521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152155</t>
+          <t>151923</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>143418</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>154902</t>
+          <t>154813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>290174</t>
+          <t>287970</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>305638</t>
+          <t>304309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32615</t>
+          <t>34819</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49275</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29136</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12242</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>23778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8776</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,25%</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>29210</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42976</t>
+          <t>43243</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
